--- a/活頁簿1.xlsx
+++ b/活頁簿1.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AI\Taifex\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FA227CA-C4B4-42F9-A712-BD16EDCCCD95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A549191B-1DCB-4A4E-A8B0-FCD34141731C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{1B686970-2E57-4EE1-A69A-E290CE23ECCF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{1B686970-2E57-4EE1-A69A-E290CE23ECCF}"/>
   </bookViews>
   <sheets>
-    <sheet name="工作表1" sheetId="1" r:id="rId1"/>
-    <sheet name="工作表1 (2)" sheetId="2" r:id="rId2"/>
+    <sheet name="工作表1 (2)" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -86,6 +85,10 @@
   </si>
   <si>
     <t xml:space="preserve"> 查當日資料 當日無資料 轉查前一個交易日資料</t>
+  </si>
+  <si>
+    <t>2026.01.20 06:50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -109,12 +112,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -131,8 +140,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -158,7 +170,7 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>781050</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="7390476" cy="6123809"/>
@@ -195,10 +207,10 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>333375</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>514350</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="7076190" cy="9885714"/>
     <xdr:pic>
@@ -222,7 +234,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3762375" y="7429500"/>
+          <a:off x="12849225" y="6134100"/>
           <a:ext cx="7076190" cy="9885714"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -236,7 +248,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>63</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="14485714" cy="7085714"/>
@@ -271,6 +283,50 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>207987</xdr:colOff>
+      <xdr:row>137</xdr:row>
+      <xdr:rowOff>113243</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="圖片 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9A4FBF7-3690-A63F-4874-EAE5A1E38129}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1409700" y="20364450"/>
+          <a:ext cx="12504762" cy="8457143"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -570,111 +626,107 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36172A45-A7E2-4DDD-B105-93C473059EFA}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{640030C1-34BB-48B4-AD4E-7EC6DA4F9FB9}">
-  <dimension ref="C14:C32"/>
+  <dimension ref="C3:C95"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="143.875" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="3" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
+        <v>7</v>
+      </c>
+    </row>
     <row r="14" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>16</v>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C16" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C17" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C19" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C21" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C22" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="23" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C23" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C24" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C25" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C26" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C27" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C28" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C29" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C30" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C31" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C32" t="s">
         <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:3" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C95" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/活頁簿1.xlsx
+++ b/活頁簿1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AI\Taifex\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A549191B-1DCB-4A4E-A8B0-FCD34141731C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14544423-91D2-4F51-B880-FA1AA6E3FB41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{1B686970-2E57-4EE1-A69A-E290CE23ECCF}"/>
   </bookViews>
